--- a/reports/login-test-cases-execution-report.xlsx
+++ b/reports/login-test-cases-execution-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2290" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="476">
   <si>
     <t>Excel Execution Report</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-09-02T13:48:47.521Z</t>
+    <t>2026-09-03T10:49:03.432Z</t>
   </si>
   <si>
     <t>Source workbook modified</t>
@@ -1037,10 +1037,118 @@
     <t>Activity — heading contains "A comprehensive visual overview of bug status, trends, and metrics for effective monitoring and analysis."</t>
   </si>
   <si>
-    <t>generated/TC_LOGIN_139.spec.ts</t>
-  </si>
-  <si>
-    <t>2026-09-02T13:48:30.350Z</t>
+    <t>tests-e2e/generated/TC_LOGIN_139.spec.ts</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_140</t>
+  </si>
+  <si>
+    <t>Activity — #critical_bugs_moving contains "Rate at Which Critical Issues are Closed"</t>
+  </si>
+  <si>
+    <t>tests-e2e/generated/TC_LOGIN_140.spec.ts</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_141</t>
+  </si>
+  <si>
+    <t>#tr_1751001 &gt; .tabulator-cell.tabulator-cell--checkbox &gt; .rounded-checkbox-cont &gt; .rounded-checkbox-ui — #ap_notifications_panel contains "Notification Preferences"</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_142</t>
+  </si>
+  <si>
+    <t>Notifications Notifications — #requirements_banner contains "Requirements management need not be hard"</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_143</t>
+  </si>
+  <si>
+    <t>Close — heading contains "A comprehensive visual overview of bug status, trends, and metrics for effective monitoring and analysis."</t>
+  </si>
+  <si>
+    <t>tests-e2e/generated/TC_LOGIN_143.spec.ts</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_144</t>
+  </si>
+  <si>
+    <t>#tr_1751001 &gt; .tabulator-cell.tabulator-cell--checkbox &gt; .rounded-checkbox-cont &gt; .rounded-checkbox-ui — #show_all_teams contains "Sravya D"</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_145</t>
+  </si>
+  <si>
+    <t>tests-e2e/generated/TC_LOGIN_145.spec.ts</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_146</t>
+  </si>
+  <si>
+    <t>Home — #all_apps contains "Faclon labs"</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_147</t>
+  </si>
+  <si>
+    <t>Create Project — #main-content contains "Test1"</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_148</t>
+  </si>
+  <si>
+    <t>+ Create Project</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_149</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_150</t>
+  </si>
+  <si>
+    <t>+ Create Project — #first_report_modal contains "Create New Project"</t>
+  </si>
+  <si>
+    <t>tests-e2e/generated/TC_LOGIN_150.spec.ts</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_151</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_152</t>
+  </si>
+  <si>
+    <t>Following — #bug_report_multi_search contains "0"</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_153</t>
+  </si>
+  <si>
+    <t>Team Projects — #all_apps contains "Faclon labs"</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_154</t>
+  </si>
+  <si>
+    <t>Drafts (3)  — Draft is visible</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_155</t>
+  </si>
+  <si>
+    <t>Search — #all_apps contains "Faclon labs"</t>
+  </si>
+  <si>
+    <t>tests-e2e/generated/TC_LOGIN_155.spec.ts</t>
+  </si>
+  <si>
+    <t>TC_LOGIN_156</t>
+  </si>
+  <si>
+    <t>Activity — #tc_update_status_1755479 contains "New"</t>
+  </si>
+  <si>
+    <t>tests-e2e/generated/TC_LOGIN_156.spec.ts</t>
   </si>
   <si>
     <t>TC_PROJ_001</t>
@@ -1316,7 +1424,22 @@
     <t>TC_DASHBOARD_027</t>
   </si>
   <si>
-    <t>Activity — #critical_bugs_moving contains "Rate at Which Critical Issues are Closed"</t>
+    <t>TC_DASHBOARD_028</t>
+  </si>
+  <si>
+    <t>Reports — heading contains "A comprehensive visual overview of bug status, trends, and metrics for effective monitoring and analysis."</t>
+  </si>
+  <si>
+    <t>Error: page.goto: net::ERR_EMPTY_RESPONSE at https://my.bugasura.io/ | Call log: | - navigating to "https://my.bugasura.io/", waiting until "domcontentloaded" | Error: page.goto: net::ERR_EMPTY_RESPONSE at https://my.bugasura.io/ | Call log: | - navigating to "https://my.bugasura.io/", waiting until "domcontentloaded"</t>
+  </si>
+  <si>
+    <t>Passed (flaky - passed on retry)</t>
+  </si>
+  <si>
+    <t>generated/TC_DASHBOARD_028.spec.ts</t>
+  </si>
+  <si>
+    <t>2026-09-03T10:48:46.958Z</t>
   </si>
 </sst>
 </file>
@@ -1812,7 +1935,7 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>173</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1820,7 +1943,7 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1828,7 +1951,7 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1836,7 +1959,7 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1884,7 +2007,7 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>172</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1900,7 +2023,7 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1927,7 +2050,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M174"/>
+  <dimension ref="A1:M192"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -7275,59 +7398,59 @@
         <v>47</v>
       </c>
     </row>
-    <row r="131" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="7" t="s">
+    <row r="131" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B131" s="7" t="s">
+      <c r="B131" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C131" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E131" s="7" t="s">
+      <c r="C131" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E131" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F131" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G131" s="7">
-        <v>15.09</v>
-      </c>
-      <c r="H131" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I131" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J131" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="K131" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L131" s="7" t="s">
+      <c r="F131" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H131" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I131" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J131" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K131" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L131" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="M131" s="7" t="s">
-        <v>342</v>
+      <c r="M131" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="132" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B132" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B132" s="5" t="s">
-        <v>344</v>
-      </c>
       <c r="C132" s="5" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E132" s="5" t="s">
         <v>73</v>
@@ -7351,7 +7474,7 @@
         <v>46</v>
       </c>
       <c r="L132" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="M132" s="5" t="s">
         <v>47</v>
@@ -7359,19 +7482,19 @@
     </row>
     <row r="133" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="B133" s="5" t="s">
-        <v>347</v>
-      </c>
       <c r="C133" s="5" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>46</v>
@@ -7392,7 +7515,7 @@
         <v>46</v>
       </c>
       <c r="L133" s="5" t="s">
-        <v>345</v>
+        <v>47</v>
       </c>
       <c r="M133" s="5" t="s">
         <v>47</v>
@@ -7400,19 +7523,19 @@
     </row>
     <row r="134" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B134" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="B134" s="5" t="s">
-        <v>349</v>
-      </c>
       <c r="C134" s="5" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>46</v>
@@ -7433,7 +7556,7 @@
         <v>46</v>
       </c>
       <c r="L134" s="5" t="s">
-        <v>345</v>
+        <v>47</v>
       </c>
       <c r="M134" s="5" t="s">
         <v>47</v>
@@ -7441,16 +7564,16 @@
     </row>
     <row r="135" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B135" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="B135" s="5" t="s">
-        <v>351</v>
-      </c>
       <c r="C135" s="5" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>15</v>
@@ -7474,7 +7597,7 @@
         <v>46</v>
       </c>
       <c r="L135" s="5" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="M135" s="5" t="s">
         <v>47</v>
@@ -7488,13 +7611,13 @@
         <v>353</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>46</v>
@@ -7515,7 +7638,7 @@
         <v>46</v>
       </c>
       <c r="L136" s="5" t="s">
-        <v>345</v>
+        <v>47</v>
       </c>
       <c r="M136" s="5" t="s">
         <v>47</v>
@@ -7526,13 +7649,13 @@
         <v>354</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>355</v>
+        <v>219</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>15</v>
@@ -7556,7 +7679,7 @@
         <v>46</v>
       </c>
       <c r="L137" s="5" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="M137" s="5" t="s">
         <v>47</v>
@@ -7570,13 +7693,13 @@
         <v>357</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>358</v>
+        <v>47</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>46</v>
@@ -7597,7 +7720,7 @@
         <v>46</v>
       </c>
       <c r="L138" s="5" t="s">
-        <v>345</v>
+        <v>47</v>
       </c>
       <c r="M138" s="5" t="s">
         <v>47</v>
@@ -7605,16 +7728,16 @@
     </row>
     <row r="139" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B139" s="5" t="s">
-        <v>360</v>
-      </c>
       <c r="C139" s="5" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>78</v>
@@ -7646,16 +7769,16 @@
     </row>
     <row r="140" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B140" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="B140" s="5" t="s">
-        <v>362</v>
-      </c>
       <c r="C140" s="5" t="s">
-        <v>363</v>
+        <v>47</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>78</v>
@@ -7687,19 +7810,19 @@
     </row>
     <row r="141" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>365</v>
+        <v>99</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>46</v>
@@ -7720,7 +7843,7 @@
         <v>46</v>
       </c>
       <c r="L141" s="5" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="M141" s="5" t="s">
         <v>47</v>
@@ -7728,19 +7851,19 @@
     </row>
     <row r="142" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>46</v>
@@ -7761,7 +7884,7 @@
         <v>46</v>
       </c>
       <c r="L142" s="5" t="s">
-        <v>62</v>
+        <v>365</v>
       </c>
       <c r="M142" s="5" t="s">
         <v>47</v>
@@ -7769,19 +7892,19 @@
     </row>
     <row r="143" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>46</v>
@@ -7802,7 +7925,7 @@
         <v>46</v>
       </c>
       <c r="L143" s="5" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="M143" s="5" t="s">
         <v>47</v>
@@ -7810,19 +7933,19 @@
     </row>
     <row r="144" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>46</v>
@@ -7843,7 +7966,7 @@
         <v>46</v>
       </c>
       <c r="L144" s="5" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="M144" s="5" t="s">
         <v>47</v>
@@ -7851,19 +7974,19 @@
     </row>
     <row r="145" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>46</v>
@@ -7884,7 +8007,7 @@
         <v>46</v>
       </c>
       <c r="L145" s="5" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="M145" s="5" t="s">
         <v>47</v>
@@ -7892,19 +8015,19 @@
     </row>
     <row r="146" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>46</v>
@@ -7925,7 +8048,7 @@
         <v>46</v>
       </c>
       <c r="L146" s="5" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="M146" s="5" t="s">
         <v>47</v>
@@ -7933,16 +8056,16 @@
     </row>
     <row r="147" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E147" s="5" t="s">
         <v>15</v>
@@ -7966,7 +8089,7 @@
         <v>46</v>
       </c>
       <c r="L147" s="5" t="s">
-        <v>62</v>
+        <v>375</v>
       </c>
       <c r="M147" s="5" t="s">
         <v>47</v>
@@ -7974,16 +8097,16 @@
     </row>
     <row r="148" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>380</v>
+        <v>47</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E148" s="5" t="s">
         <v>15</v>
@@ -8007,7 +8130,7 @@
         <v>46</v>
       </c>
       <c r="L148" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="M148" s="5" t="s">
         <v>47</v>
@@ -8015,19 +8138,19 @@
     </row>
     <row r="149" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>46</v>
@@ -8048,7 +8171,7 @@
         <v>46</v>
       </c>
       <c r="L149" s="5" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="M149" s="5" t="s">
         <v>47</v>
@@ -8056,19 +8179,19 @@
     </row>
     <row r="150" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>46</v>
@@ -8089,7 +8212,7 @@
         <v>46</v>
       </c>
       <c r="L150" s="5" t="s">
-        <v>47</v>
+        <v>381</v>
       </c>
       <c r="M150" s="5" t="s">
         <v>47</v>
@@ -8097,19 +8220,19 @@
     </row>
     <row r="151" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>46</v>
@@ -8130,7 +8253,7 @@
         <v>46</v>
       </c>
       <c r="L151" s="5" t="s">
-        <v>47</v>
+        <v>381</v>
       </c>
       <c r="M151" s="5" t="s">
         <v>47</v>
@@ -8138,19 +8261,19 @@
     </row>
     <row r="152" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>46</v>
@@ -8171,7 +8294,7 @@
         <v>46</v>
       </c>
       <c r="L152" s="5" t="s">
-        <v>47</v>
+        <v>381</v>
       </c>
       <c r="M152" s="5" t="s">
         <v>47</v>
@@ -8179,19 +8302,19 @@
     </row>
     <row r="153" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>46</v>
@@ -8212,7 +8335,7 @@
         <v>46</v>
       </c>
       <c r="L153" s="5" t="s">
-        <v>47</v>
+        <v>381</v>
       </c>
       <c r="M153" s="5" t="s">
         <v>47</v>
@@ -8220,16 +8343,16 @@
     </row>
     <row r="154" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>207</v>
+        <v>391</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>15</v>
@@ -8253,7 +8376,7 @@
         <v>46</v>
       </c>
       <c r="L154" s="5" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="M154" s="5" t="s">
         <v>47</v>
@@ -8261,19 +8384,19 @@
     </row>
     <row r="155" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>219</v>
+        <v>393</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>47</v>
+        <v>394</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>46</v>
@@ -8294,7 +8417,7 @@
         <v>46</v>
       </c>
       <c r="L155" s="5" t="s">
-        <v>47</v>
+        <v>381</v>
       </c>
       <c r="M155" s="5" t="s">
         <v>47</v>
@@ -8302,19 +8425,19 @@
     </row>
     <row r="156" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="B156" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="B156" s="5" t="s">
-        <v>397</v>
-      </c>
       <c r="C156" s="5" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>46</v>
@@ -8335,7 +8458,7 @@
         <v>46</v>
       </c>
       <c r="L156" s="5" t="s">
-        <v>398</v>
+        <v>47</v>
       </c>
       <c r="M156" s="5" t="s">
         <v>47</v>
@@ -8343,19 +8466,19 @@
     </row>
     <row r="157" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C157" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B157" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="D157" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>46</v>
@@ -8376,7 +8499,7 @@
         <v>46</v>
       </c>
       <c r="L157" s="5" t="s">
-        <v>401</v>
+        <v>47</v>
       </c>
       <c r="M157" s="5" t="s">
         <v>47</v>
@@ -8384,19 +8507,19 @@
     </row>
     <row r="158" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>283</v>
+        <v>401</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>46</v>
@@ -8417,7 +8540,7 @@
         <v>46</v>
       </c>
       <c r="L158" s="5" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M158" s="5" t="s">
         <v>47</v>
@@ -8425,16 +8548,16 @@
     </row>
     <row r="159" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="B159" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B159" s="5" t="s">
-        <v>404</v>
-      </c>
       <c r="C159" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E159" s="5" t="s">
         <v>15</v>
@@ -8458,7 +8581,7 @@
         <v>46</v>
       </c>
       <c r="L159" s="5" t="s">
-        <v>405</v>
+        <v>62</v>
       </c>
       <c r="M159" s="5" t="s">
         <v>47</v>
@@ -8466,19 +8589,19 @@
     </row>
     <row r="160" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>184</v>
+        <v>405</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>46</v>
@@ -8499,7 +8622,7 @@
         <v>46</v>
       </c>
       <c r="L160" s="5" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M160" s="5" t="s">
         <v>47</v>
@@ -8507,16 +8630,16 @@
     </row>
     <row r="161" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B161" s="5" t="s">
-        <v>408</v>
-      </c>
       <c r="C161" s="5" t="s">
-        <v>380</v>
+        <v>44</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E161" s="5" t="s">
         <v>15</v>
@@ -8540,7 +8663,7 @@
         <v>46</v>
       </c>
       <c r="L161" s="5" t="s">
-        <v>409</v>
+        <v>62</v>
       </c>
       <c r="M161" s="5" t="s">
         <v>47</v>
@@ -8548,19 +8671,19 @@
     </row>
     <row r="162" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>222</v>
+        <v>409</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>380</v>
+        <v>44</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>46</v>
@@ -8581,7 +8704,7 @@
         <v>46</v>
       </c>
       <c r="L162" s="5" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M162" s="5" t="s">
         <v>47</v>
@@ -8589,13 +8712,13 @@
     </row>
     <row r="163" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B163" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B163" s="5" t="s">
-        <v>408</v>
-      </c>
       <c r="C163" s="5" t="s">
-        <v>380</v>
+        <v>44</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>45</v>
@@ -8622,7 +8745,7 @@
         <v>46</v>
       </c>
       <c r="L163" s="5" t="s">
-        <v>412</v>
+        <v>62</v>
       </c>
       <c r="M163" s="5" t="s">
         <v>47</v>
@@ -8630,16 +8753,16 @@
     </row>
     <row r="164" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="B164" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B164" s="5" t="s">
-        <v>414</v>
-      </c>
       <c r="C164" s="5" t="s">
-        <v>380</v>
+        <v>44</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="E164" s="5" t="s">
         <v>15</v>
@@ -8663,7 +8786,7 @@
         <v>46</v>
       </c>
       <c r="L164" s="5" t="s">
-        <v>415</v>
+        <v>62</v>
       </c>
       <c r="M164" s="5" t="s">
         <v>47</v>
@@ -8671,13 +8794,13 @@
     </row>
     <row r="165" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C165" s="5" t="s">
         <v>416</v>
-      </c>
-      <c r="B165" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>380</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>45</v>
@@ -8704,7 +8827,7 @@
         <v>46</v>
       </c>
       <c r="L165" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M165" s="5" t="s">
         <v>47</v>
@@ -8712,13 +8835,13 @@
     </row>
     <row r="166" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B166" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B166" s="5" t="s">
-        <v>417</v>
-      </c>
       <c r="C166" s="5" t="s">
-        <v>380</v>
+        <v>44</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>45</v>
@@ -8756,13 +8879,13 @@
         <v>421</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>212</v>
+        <v>422</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E167" s="5" t="s">
         <v>78</v>
@@ -8794,10 +8917,10 @@
     </row>
     <row r="168" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>47</v>
@@ -8835,10 +8958,10 @@
     </row>
     <row r="169" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>259</v>
+        <v>426</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>47</v>
@@ -8876,10 +8999,10 @@
     </row>
     <row r="170" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>298</v>
+        <v>428</v>
       </c>
       <c r="C170" s="5" t="s">
         <v>47</v>
@@ -8917,10 +9040,10 @@
     </row>
     <row r="171" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>427</v>
+        <v>207</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>47</v>
@@ -8929,7 +9052,7 @@
         <v>47</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>46</v>
@@ -8950,7 +9073,7 @@
         <v>46</v>
       </c>
       <c r="L171" s="5" t="s">
-        <v>47</v>
+        <v>430</v>
       </c>
       <c r="M171" s="5" t="s">
         <v>47</v>
@@ -8958,7 +9081,7 @@
     </row>
     <row r="172" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>219</v>
@@ -8970,7 +9093,7 @@
         <v>47</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>46</v>
@@ -8991,7 +9114,7 @@
         <v>46</v>
       </c>
       <c r="L172" s="5" t="s">
-        <v>429</v>
+        <v>47</v>
       </c>
       <c r="M172" s="5" t="s">
         <v>47</v>
@@ -8999,10 +9122,10 @@
     </row>
     <row r="173" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>47</v>
@@ -9032,7 +9155,7 @@
         <v>46</v>
       </c>
       <c r="L173" s="5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M173" s="5" t="s">
         <v>47</v>
@@ -9040,43 +9163,781 @@
     </row>
     <row r="174" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>380</v>
+        <v>47</v>
       </c>
       <c r="D174" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H174" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I174" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J174" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K174" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L174" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="M174" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G175" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H175" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I175" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J175" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K175" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L175" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M175" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I176" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J176" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K176" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L176" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="M176" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H177" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I177" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J177" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K177" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L177" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M177" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E178" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H178" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I178" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J178" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K178" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L178" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="M178" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G179" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H179" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I179" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J179" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K179" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L179" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M179" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D180" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E174" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H174" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I174" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J174" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K174" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L174" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="M174" s="5" t="s">
-        <v>47</v>
+      <c r="E180" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H180" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I180" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J180" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K180" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L180" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="M180" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H181" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I181" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J181" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K181" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L181" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="M181" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H182" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I182" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J182" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K182" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L182" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="M182" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E183" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G183" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H183" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I183" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J183" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K183" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L183" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="M183" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E184" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G184" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H184" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I184" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J184" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K184" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L184" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M184" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H185" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I185" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J185" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K185" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L185" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M185" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H186" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I186" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J186" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K186" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L186" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M186" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H187" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I187" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J187" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K187" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L187" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M187" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H188" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I188" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J188" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K188" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L188" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M188" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E189" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F189" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G189" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H189" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I189" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J189" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K189" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L189" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="M189" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E190" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F190" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G190" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H190" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I190" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J190" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K190" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L190" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="M190" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G191" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H191" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I191" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J191" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K191" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L191" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M191" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F192" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G192" s="7">
+        <v>15.85</v>
+      </c>
+      <c r="H192" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="I192" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J192" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K192" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="L192" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="M192" s="7" t="s">
+        <v>475</v>
       </c>
     </row>
   </sheetData>
